--- a/BV Historical Data.xlsx
+++ b/BV Historical Data.xlsx
@@ -180,7 +180,7 @@
             <rFont val="Arial"/>
             <scheme val="minor"/>
           </rPr>
-          <t>SY 9 for 0% economic return</t>
+          <t>9 for 0% economic return</t>
         </r>
       </text>
     </comment>
